--- a/artfynd/A 40578-2021 artfynd.xlsx
+++ b/artfynd/A 40578-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40578-2021 artfynd.xlsx
+++ b/artfynd/A 40578-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97120076</v>
+        <v>97120042</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509837.7017715109</v>
+        <v>509841</v>
       </c>
       <c r="R2" t="n">
-        <v>6698057.335154233</v>
+        <v>6698077</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -761,7 +756,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -771,7 +766,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ca. 1 kvm.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,15 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97120042</v>
+        <v>97120076</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,7 +828,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509841.1125172437</v>
+        <v>509837</v>
       </c>
       <c r="R3" t="n">
-        <v>6698076.606668666</v>
+        <v>6698057</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -884,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,12 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ca. 1 kvm.</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,12 +919,7 @@
         <v>97120054</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -968,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509838.6778046566</v>
+        <v>509839</v>
       </c>
       <c r="R4" t="n">
-        <v>6698062.276852773</v>
+        <v>6698063</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>

--- a/artfynd/A 40578-2021 artfynd.xlsx
+++ b/artfynd/A 40578-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97120042</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -913,6 +923,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97120076</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1027,8 +1042,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97120054</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>